--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>76/100</t>
+          <t>78/100</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Maclès Immobilier vous propose à la vente un local commercial de 65 m², situé à Saint-Denis (93), vendu occupé dans le cadre d’un bail commercial 3/6/9 récemment signé. Le bien développe une surface d’environ 65 m² et bénéficie d’un agencement fonctionnel pour une activité commerciale. Il dispose notamment d’un WC ainsi que d’une réserve en sous-sol, offrant un espace de stockage complémentaire. Le local est actuellement loué moyennant un loyer mensuel de 1 400 € HT, soit 16 800 € HT par an. La signature récente du bail offre à l’acquéreur une visibilité locative intéressante dès l’acquisition</t>
+          <t>Maclès Immobilier vous propose à la vente un local commercial de 65 m², situé à Saint-Denis (93), vendu occupé dans le cadre d’un bail commercial 3/6/9 récemment signé. Le bien développe une surface d’environ 65 m² et bénéficie d’un agencement fonctionnel pour une activité commerciale. Il dispose notamment d’un WC ainsi que d’une réserve en sous-sol, offrant un espace de stockage complémentaire. Le local est actuellement loué moyennant un loyer mensuel de 1 400 € HT, soit 16 800 € HT par an. La signature récente du bail offre à l’acquéreur une visibilité locative intéressante dès l’acquisition. Caractéristiques principales : Surface : 65 m² de surface commerciale environ Local commercial vendu occupé Bail commercial 3/6/9 récemment signé Loyer : 1 400 € HT/mois Loyer annuel : 16 800 € HT WC Réserve en sous-sol Prix de vente : 185 000 € Sur la base du prix de vente affiché, le bien présente une rentabilité brute d’environ 9,1 %, avant prise en compte des frais d’acquisition, charges, fiscalité et éventuels honoraires. Une opportunité particulièrement adaptée à un investisseur recherchant un actif commercial déjà loué, avec un bail récent et un rendement attractif à Saint-Denis. Pour obtenir davantage d'informations sur le bail, les conditions locatives ou organiser une visite, contactez Maclès Immobilier.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Maclès Immobilier vous propose à la vente un local commercial de 65 m², situé à Saint-Denis (93), vendu occupé dans le cadre d’un bail commercial 3/6/9 récemment signé. Le bien développe une surface d’environ 65 m² et bénéficie d’un agencement fonctionnel pour une activité commerciale. Il dispose notamment d’un WC ainsi que d’une réserve en sous-sol, offrant un espace de stockage complémentaire. Le local est actuellement loué moyennant un loyer mensuel de 1 400 € HT, soit 16 800 € HT par an. La signature récente du bail offre à l’acquéreur une visibilité locative intéressante dès l’acquisition. Caractéristiques principales : Surface : 65 m² de surface commerciale environ Local commercial vendu occupé Bail commercial 3/6/9 récemment signé Loyer : 1 400 € HT/mois Loyer annuel : 16 800 € HT WC Réserve en sous-sol Prix de vente : 185 000 € Sur la base du prix de vente affiché, le bien présente une rentabilité brute d’environ 9,1 %, avant prise en compte des frais d’acquisition, charges, fiscalité et éventuels honoraires. Une opportunité particulièrement adaptée à un investisseur recherchant un actif commercial déjà loué, avec un bail récent et un rendement attractif à Saint-Denis. Pour obtenir davantage d'informations sur le bail, les conditions locatives ou organiser une visite, contactez Maclès Immobilier.</t>
+          <t>À VENDRE – LOCAL COMMERCIAL LOUÉ – SAINT-DENIS (93) – INVESTISSEMENT LOCATIF Maclès Immobilier vous propose à la vente un local commercial de 65 m², situé à Saint-Denis (93), vendu occupé dans le cadre d’un bail commercial 3/6/9 récemment signé. Le bien développe une surface d’environ 65 m² et bénéficie d’un agencement fonctionnel pour une activité commerciale. Il dispose notamment d’un WC ainsi que d’une réserve en sous-sol, offrant un espace de stockage complémentaire. Le local est actuellement loué moyennant un loyer mensuel de 1 400 € HT, soit 16 800 € HT par an. La signature récente du bail offre à l’acquéreur une visibilité locative intéressante dès l’acquisition. Caractéristiques principales : Surface : 65 m² de surface commerciale environ Local commercial vendu occupé Bail commercial 3/6/9 récemment signé Loyer : 1 400 € HT/mois Loyer annuel : 16 800 € HT WC Réserve en sous-sol Prix de vente : 185 000 € Sur la base du prix de vente affiché, le bien présente une rentabilité brute d’environ 9,1 %, avant prise en compte des frais d’acquisition, charges, fiscalité et éventuels honoraires. Une opportunité particulièrement adaptée à un investisseur recherchant un actif commercial déjà loué, avec un bail récent et un rendement attractif à Saint-Denis. Pour obtenir davantage d'informations sur le bail, les conditions locatives ou organiser une visite, contactez Maclès Immobilier.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +155 €/mois.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +142 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-saint-denis-71d97990.xlsx
+++ b/docs/dossiers/dossier-saint-denis-71d97990.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
